--- a/artfynd/A 16095-2026 artfynd.xlsx
+++ b/artfynd/A 16095-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118755862</v>
       </c>
       <c r="B2" t="n">
-        <v>57833</v>
+        <v>57834</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16095-2026 artfynd.xlsx
+++ b/artfynd/A 16095-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118755862</v>
       </c>
       <c r="B2" t="n">
-        <v>57834</v>
+        <v>57838</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16095-2026 artfynd.xlsx
+++ b/artfynd/A 16095-2026 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>118755862</v>
       </c>
       <c r="B2" t="n">
-        <v>57838</v>
+        <v>57860</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">

--- a/artfynd/A 16095-2026 artfynd.xlsx
+++ b/artfynd/A 16095-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,6 +774,536 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135521872</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98623</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220007</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Missne</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Calla palustris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Djurgården 450 m N, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>605507</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6553544</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hyltinge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Mosse</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135521802</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106358</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Djurgården 450 m N, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>605507</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6553544</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hyltinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135521947</v>
+      </c>
+      <c r="B5" t="n">
+        <v>103764</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222004</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kärrviol</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Viola palustris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Djurgården 450 m N, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>605507</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6553544</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hyltinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Mosse</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135521992</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99853</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222306</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Stjärnstarr</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carex echinata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Murray</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Djurgården 450 m N, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>605507</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6553544</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hyltinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Mosse</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135522133</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100241</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222654</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Brunag</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Rhynchospora fusca</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) W. T. Aiton</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Djurgården 450 m N, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>605507</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6553544</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hyltinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Mosse</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16095-2026 artfynd.xlsx
+++ b/artfynd/A 16095-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118755862</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135521872</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135521802</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,6 +1109,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135521947</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1196,6 +1221,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135521992</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1303,8 +1333,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135522133</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 16095-2026 artfynd.xlsx
+++ b/artfynd/A 16095-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135521872</v>
       </c>
       <c r="B3" t="n">
-        <v>98623</v>
+        <v>98670</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>135521802</v>
       </c>
       <c r="B4" t="n">
-        <v>106358</v>
+        <v>106413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>135521947</v>
       </c>
       <c r="B5" t="n">
-        <v>103764</v>
+        <v>103815</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>135521992</v>
       </c>
       <c r="B6" t="n">
-        <v>99853</v>
+        <v>99900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>135522133</v>
       </c>
       <c r="B7" t="n">
-        <v>100241</v>
+        <v>100288</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 16095-2026 artfynd.xlsx
+++ b/artfynd/A 16095-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135521872</v>
       </c>
       <c r="B3" t="n">
-        <v>98670</v>
+        <v>98697</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>135521802</v>
       </c>
       <c r="B4" t="n">
-        <v>106413</v>
+        <v>106440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>135521947</v>
       </c>
       <c r="B5" t="n">
-        <v>103815</v>
+        <v>103842</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>135521992</v>
       </c>
       <c r="B6" t="n">
-        <v>99900</v>
+        <v>99927</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>135522133</v>
       </c>
       <c r="B7" t="n">
-        <v>100288</v>
+        <v>100315</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 16095-2026 artfynd.xlsx
+++ b/artfynd/A 16095-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,9 +784,569 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135521872</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98702</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220007</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Missne</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Calla palustris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Djurgården 450 m N, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>605507</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6553544</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hyltinge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Mosse</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135521872</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135521802</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106445</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Djurgården 450 m N, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>605507</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6553544</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hyltinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135521802</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135521947</v>
+      </c>
+      <c r="B5" t="n">
+        <v>103847</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222004</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kärrviol</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Viola palustris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Djurgården 450 m N, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>605507</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6553544</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hyltinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Mosse</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135521947</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135521992</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99932</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222306</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Stjärnstarr</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carex echinata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Murray</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Djurgården 450 m N, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>605507</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6553544</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hyltinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Mosse</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135521992</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135522133</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100320</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222654</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Brunag</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Rhynchospora fusca</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) W. T. Aiton</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Djurgården 450 m N, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>605507</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6553544</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hyltinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Mosse</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135522133</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16095-2026 artfynd.xlsx
+++ b/artfynd/A 16095-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135521872</v>
       </c>
       <c r="B3" t="n">
-        <v>98702</v>
+        <v>98704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>135521802</v>
       </c>
       <c r="B4" t="n">
-        <v>106445</v>
+        <v>106447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>135521947</v>
       </c>
       <c r="B5" t="n">
-        <v>103847</v>
+        <v>103849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>135521992</v>
       </c>
       <c r="B6" t="n">
-        <v>99932</v>
+        <v>99934</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>135522133</v>
       </c>
       <c r="B7" t="n">
-        <v>100320</v>
+        <v>100322</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 16095-2026 artfynd.xlsx
+++ b/artfynd/A 16095-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135521872</v>
       </c>
       <c r="B3" t="n">
-        <v>98704</v>
+        <v>98721</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>135521802</v>
       </c>
       <c r="B4" t="n">
-        <v>106447</v>
+        <v>106467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>135521947</v>
       </c>
       <c r="B5" t="n">
-        <v>103849</v>
+        <v>103869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>135521992</v>
       </c>
       <c r="B6" t="n">
-        <v>99934</v>
+        <v>99951</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>135522133</v>
       </c>
       <c r="B7" t="n">
-        <v>100322</v>
+        <v>100339</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 16095-2026 artfynd.xlsx
+++ b/artfynd/A 16095-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135521872</v>
       </c>
       <c r="B3" t="n">
-        <v>98721</v>
+        <v>98722</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>135521802</v>
       </c>
       <c r="B4" t="n">
-        <v>106467</v>
+        <v>106469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>135521947</v>
       </c>
       <c r="B5" t="n">
-        <v>103869</v>
+        <v>103871</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>135521992</v>
       </c>
       <c r="B6" t="n">
-        <v>99951</v>
+        <v>99953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>135522133</v>
       </c>
       <c r="B7" t="n">
-        <v>100339</v>
+        <v>100341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
